--- a/output/2026-10-04_09_Malesia_Sarawak_Cleaning.xlsx
+++ b/output/2026-10-04_09_Malesia_Sarawak_Cleaning.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Confermato via fetch diretto: pagina dedicata Kuching elenca detergenti, disinfettanti, utensili per pulizia, floor-care per facility contractor a Sarawak. E' un marketplace aggregatore B2B (10.000+ fornitori), non un distributore mono-brand classico: valutare adattabilita' al modello di canale Dupuy.</t>
+          <t>Confermato via fetch diretto: pagina dedicata Kuching elenca detergenti, disinfettanti, utensili per pulizia, floor-care per facility contractor a Sarawak. E' un marketplace aggregatore B2B (10.000+ fornitori), non un distributore mono-brand classico: valutare adattabilita' al modello di canale Dupuy. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -535,11 +535,9 @@
           <t>Cleaning - spazzatrici industriali/stradali/aeroportuali</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Esistenza confermata (membro Camera di Commercio Malese-Tedesca, fondata 1996). Distributore di Bucher Municipal, Hako, Minuteman, DISAB-TELLA (DISAB = aspirazione industriale, forte coerenza col core business Dupuy). Verificare copertura diretta su Sarawak.</t>
+          <t>Esistenza confermata (membro Camera di Commercio Malese-Tedesca, fondata 1996). Distributore di Bucher Municipal, Hako, Minuteman, DISAB-TELLA (DISAB = aspirazione industriale, forte coerenza col core business Dupuy). Verificare copertura diretta su Sarawak. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -554,7 +552,6 @@
           <t>Klenco (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Bukit Naga Industrial Park, Shah Alam, Selangor. Nessuna filiale Sarawak confermata</t>
@@ -565,11 +562,9 @@
           <t>Cleaning - distributore macchine/utensili/chimici pulizia industriale/municipale</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Esistenza e attivita' confermate (dal 1971, leader regionale SEA, certificazioni ISO 9001/14001, premio ISSA). Nessun riscontro di presenza diretta a Sarawak.</t>
+          <t>Esistenza e attivita' confermate (dal 1971, leader regionale SEA, certificazioni ISO 9001/14001, premio ISSA). Nessun riscontro di presenza diretta a Sarawak. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -604,10 +599,9 @@
           <t>+603 6420 8200</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Confermato gruppo industriale reale, divisione UMW Industries distribuisce Tennant in Malesia.</t>
+          <t>Confermato gruppo industriale reale, divisione UMW Industries distribuisce Tennant in Malesia. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -637,11 +631,9 @@
           <t>Cleaning - rivenditore autorizzato Karcher (incl. aspiratori wet&amp;dry)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Esistenza confermata, rivenditore autorizzato Karcher con garanzia locale. Attivo dal 2007.</t>
+          <t>Esistenza confermata, rivenditore autorizzato Karcher con garanzia locale. Attivo dal 2007. [DUPLICATO — vedi anche: 2026-10-03_11_Malesia_Perlis_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -656,7 +648,6 @@
           <t>Floormac (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Subang Jaya, Selangor. Copertura Sarawak non confermata</t>
@@ -667,11 +658,9 @@
           <t>Cleaning - importatore/distributore attrezzature pulizia pavimenti/heavy duty</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Esistenza confermata (SSM No. 201801018274). Distributore autorizzato Nilfisk (marchio leader aspirazione industriale), RCM, FASA, 3M, Ren Escalator Cleaning Tools. Alta coerenza col settore.</t>
+          <t>Esistenza confermata (SSM No. 201801018274). Distributore autorizzato Nilfisk (marchio leader aspirazione industriale), RCM, FASA, 3M, Ren Escalator Cleaning Tools. Alta coerenza col settore. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
